--- a/Pelada_do_Filhao.xlsx
+++ b/Pelada_do_Filhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\85223166\Desktop\Controle Pelada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC90318-1FEA-4FCD-8B7F-60349784D4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF987D0-EF45-400D-8399-09E9C91B463D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="⚙️ Config" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,11 @@
     <sheet name="🟧 Assistencias_Mes" sheetId="5" r:id="rId6"/>
     <sheet name="📅 Historico" sheetId="6" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🟥 Jogadores_Mes'!$A$2:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'🟧 Assistencias_Mes'!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🟨 Artilharia_Mes'!$A$2:$D$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="172">
   <si>
     <t>⚽  PELADA DO FILHÃO — BASE DE DADOS</t>
   </si>
@@ -155,9 +160,6 @@
     <t>data_ultima_pelada</t>
   </si>
   <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
     <t>🟥 JOGADORES DO MÊS — atualizar a cada pelada</t>
   </si>
   <si>
@@ -413,36 +415,6 @@
     <t>Presenças</t>
   </si>
   <si>
-    <t>1°</t>
-  </si>
-  <si>
-    <t>2°</t>
-  </si>
-  <si>
-    <t>3°</t>
-  </si>
-  <si>
-    <t>4°</t>
-  </si>
-  <si>
-    <t>5°</t>
-  </si>
-  <si>
-    <t>6°</t>
-  </si>
-  <si>
-    <t>7°</t>
-  </si>
-  <si>
-    <t>8°</t>
-  </si>
-  <si>
-    <t>9°</t>
-  </si>
-  <si>
-    <t>10°</t>
-  </si>
-  <si>
     <t>🟧 ASSISTÊNCIAS DO MÊS — atualizar a cada pelada</t>
   </si>
   <si>
@@ -464,9 +436,6 @@
     <t>Mai/26</t>
   </si>
   <si>
-    <t>⚽ ÚLTIMA PELADA — 14/05/2026</t>
-  </si>
-  <si>
     <t>🔵 TIME BRANCO</t>
   </si>
   <si>
@@ -482,19 +451,115 @@
     <t>4V · 1E · 1D</t>
   </si>
   <si>
-    <t>0V · 1E · 3D</t>
-  </si>
-  <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t>Rodrigao</t>
-  </si>
-  <si>
-    <t>Leo</t>
-  </si>
-  <si>
-    <t>PM</t>
+    <t xml:space="preserve">Vitor Gomide </t>
+  </si>
+  <si>
+    <t>Joao lucas</t>
+  </si>
+  <si>
+    <t>Breder</t>
+  </si>
+  <si>
+    <t>Galvao</t>
+  </si>
+  <si>
+    <t>Tutuca</t>
+  </si>
+  <si>
+    <t>Mumu</t>
+  </si>
+  <si>
+    <t>Fabio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduardo </t>
+  </si>
+  <si>
+    <t>⚽ ÚLTIMA PELADA — 21/05/2026</t>
+  </si>
+  <si>
+    <t>Galvão</t>
+  </si>
+  <si>
+    <t>João Lucas</t>
+  </si>
+  <si>
+    <t>Victor Gomide</t>
+  </si>
+  <si>
+    <t>GV</t>
+  </si>
+  <si>
+    <t>JL</t>
+  </si>
+  <si>
+    <t>TK</t>
+  </si>
+  <si>
+    <t>VG</t>
+  </si>
+  <si>
+    <t>BD</t>
+  </si>
+  <si>
+    <t>FB</t>
+  </si>
+  <si>
+    <t>1º</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego </t>
+  </si>
+  <si>
+    <t>2º</t>
+  </si>
+  <si>
+    <t>3º</t>
+  </si>
+  <si>
+    <t>Pedro Carrilho</t>
+  </si>
+  <si>
+    <t>4º</t>
+  </si>
+  <si>
+    <t>5º</t>
+  </si>
+  <si>
+    <t>6º</t>
+  </si>
+  <si>
+    <t>7º</t>
+  </si>
+  <si>
+    <t>8º</t>
+  </si>
+  <si>
+    <t>9º</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matheus Duarte </t>
+  </si>
+  <si>
+    <t>10º</t>
+  </si>
+  <si>
+    <t>Bernardo Mansoldo</t>
+  </si>
+  <si>
+    <t>11º</t>
+  </si>
+  <si>
+    <t>12º</t>
+  </si>
+  <si>
+    <t>13º</t>
+  </si>
+  <si>
+    <t>14º</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galvão </t>
   </si>
 </sst>
 </file>
@@ -504,7 +569,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -651,55 +716,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFB923C"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFCA5A5"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFDE68A"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFB91C1C"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFCCCCCC"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFBBF24"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFF87171"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFEF3C7"/>
       <name val="Georgia"/>
       <family val="1"/>
     </font>
@@ -724,8 +741,14 @@
       <name val="Georgia"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -797,6 +820,12 @@
         <fgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -825,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -917,43 +946,13 @@
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -969,7 +968,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -977,6 +976,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1292,10 +1297,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="48"/>
+      <c r="C1" s="38"/>
     </row>
     <row r="2" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="4" t="s">
@@ -1349,8 +1354,8 @@
       <c r="B8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
+      <c r="C8" s="45">
+        <v>46163</v>
       </c>
     </row>
   </sheetData>
@@ -1372,16 +1377,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="48"/>
+      <c r="B1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="38"/>
     </row>
     <row r="2" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="48"/>
+      <c r="B2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="38"/>
     </row>
     <row r="4" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
@@ -1486,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B1:D10"/>
+  <dimension ref="B1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1494,100 +1499,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="B1" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>144</v>
+      <c r="B2" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B3" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>147</v>
-      </c>
+      <c r="B3" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="36"/>
     </row>
     <row r="4" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>96</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>99</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>150</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="7" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>75</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>108</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="7" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="C10" s="5" t="s">
-        <v>151</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1600,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1611,131 +1615,131 @@
     <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+    <row r="1" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9">
+        <v>24</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="9">
+      <c r="H3" s="11">
+        <f>RANK(D3,D$3:D$32,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="12">
+        <f>IFERROR(D3/SUM(D$3:D$32),0)</f>
+        <v>0.100418410041841</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="9">
         <v>19</v>
       </c>
-      <c r="E3" s="9">
-        <v>1</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="11">
-        <f t="shared" ref="H3:H25" si="0">RANK(D3,D$3:D$25,0)</f>
-        <v>1</v>
-      </c>
-      <c r="I3" s="12">
-        <f t="shared" ref="I3:I25" si="1">IFERROR(D3/SUM(D$3:D$25),0)</f>
-        <v>0.1043956043956044</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="13">
-        <v>14</v>
-      </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>56</v>
+      <c r="E4" s="9">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="H4" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H4:H32" si="0">RANK(D4,D$3:D$32,0)</f>
         <v>2</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" si="1"/>
-        <v>7.6923076923076927E-2</v>
+        <f t="shared" ref="I4:I32" si="1">IFERROR(D4/SUM(D$3:D$32),0)</f>
+        <v>7.9497907949790794E-2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="C5" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="9">
         <v>2</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" si="0"/>
@@ -1743,30 +1747,30 @@
       </c>
       <c r="I5" s="12">
         <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <v>7.5313807531380755E-2</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="13">
+        <v>18</v>
+      </c>
+      <c r="E6" s="13">
+        <v>2</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="13">
-        <v>13</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="0"/>
@@ -1774,92 +1778,92 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <v>7.5313807531380755E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>64</v>
+      <c r="A7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="9">
-        <v>13</v>
-      </c>
-      <c r="E7" s="9">
-        <v>2</v>
-      </c>
-      <c r="F7" s="9">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>65</v>
+        <v>50</v>
+      </c>
+      <c r="D7" s="13">
+        <v>16</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" s="12">
         <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <v>6.6945606694560664E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="13">
-        <v>13</v>
-      </c>
-      <c r="E8" s="13">
-        <v>3</v>
-      </c>
-      <c r="F8" s="13">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>68</v>
+      <c r="A8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="9">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9">
+        <v>5</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" s="12">
         <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <v>6.2761506276150625E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="9">
-        <v>12</v>
-      </c>
-      <c r="E9" s="9">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>71</v>
+      <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="13">
+        <v>14</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="0"/>
@@ -1867,61 +1871,61 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" si="1"/>
-        <v>6.5934065934065936E-2</v>
+        <v>5.8577405857740586E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>51</v>
+        <v>66</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="D10" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="13">
         <v>1</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="12">
         <f t="shared" si="1"/>
-        <v>6.5934065934065936E-2</v>
+        <v>5.4393305439330547E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="0"/>
@@ -1929,80 +1933,80 @@
       </c>
       <c r="I11" s="12">
         <f t="shared" si="1"/>
-        <v>6.043956043956044E-2</v>
+        <v>5.0209205020920501E-2</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="13">
-        <v>9</v>
-      </c>
-      <c r="E12" s="13">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>80</v>
+      <c r="A12" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="9">
+        <v>12</v>
+      </c>
+      <c r="E12" s="9">
+        <v>3</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H12" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="12">
         <f t="shared" si="1"/>
-        <v>4.9450549450549448E-2</v>
+        <v>5.0209205020920501E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" si="1"/>
-        <v>4.9450549450549448E-2</v>
+        <v>4.6025104602510462E-2</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>85</v>
-      </c>
       <c r="C14" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="13">
         <v>9</v>
@@ -2014,69 +2018,69 @@
         <v>0</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H14" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="12">
         <f t="shared" si="1"/>
-        <v>4.9450549450549448E-2</v>
+        <v>3.7656903765690378E-2</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="9">
-        <v>8</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>89</v>
+      <c r="A15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="13">
+        <v>9</v>
+      </c>
+      <c r="E15" s="13">
+        <v>2</v>
+      </c>
+      <c r="F15" s="13">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" si="1"/>
-        <v>4.3956043956043959E-2</v>
+        <v>3.7656903765690378E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="13">
-        <v>6</v>
-      </c>
-      <c r="E16" s="13">
-        <v>2</v>
-      </c>
-      <c r="F16" s="13">
-        <v>1</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="A16" s="7" t="s">
         <v>92</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="9">
+        <v>8</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="0"/>
@@ -2084,61 +2088,61 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" si="1"/>
-        <v>3.2967032967032968E-2</v>
+        <v>3.3472803347280332E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="9">
-        <v>5</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="A17" s="5" t="s">
         <v>95</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="13">
+        <v>8</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I17" s="12">
         <f t="shared" si="1"/>
-        <v>2.7472527472527472E-2</v>
+        <v>3.3472803347280332E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="0"/>
@@ -2146,30 +2150,30 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" si="1"/>
-        <v>2.197802197802198E-2</v>
+        <v>2.5104602510460251E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>100</v>
+      <c r="A19" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="9">
-        <v>3</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9">
-        <v>0</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>101</v>
+        <v>54</v>
+      </c>
+      <c r="D19" s="13">
+        <v>5</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="H19" s="11">
         <f t="shared" si="0"/>
@@ -2177,61 +2181,61 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" si="1"/>
-        <v>1.6483516483516484E-2</v>
+        <v>2.0920502092050208E-2</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
-        <v>102</v>
+      <c r="A20" s="44" t="s">
+        <v>137</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>51</v>
+        <v>151</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="D20" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" s="12">
         <f t="shared" si="1"/>
-        <v>1.6483516483516484E-2</v>
+        <v>1.6736401673640166E-2</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="9">
         <v>0</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="0"/>
@@ -2239,21 +2243,21 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" si="1"/>
-        <v>1.098901098901099E-2</v>
+        <v>1.2552301255230125E-2</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>55</v>
+        <v>102</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="D22" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="13">
         <v>0</v>
@@ -2262,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="0"/>
@@ -2270,21 +2274,21 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" si="1"/>
-        <v>1.098901098901099E-2</v>
+        <v>1.2552301255230125E-2</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="9">
         <v>0</v>
@@ -2293,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="0"/>
@@ -2301,30 +2305,30 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" si="1"/>
-        <v>5.4945054945054949E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>51</v>
+        <v>108</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="D24" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="13">
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H24" s="11">
         <f t="shared" si="0"/>
@@ -2332,63 +2336,285 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" si="1"/>
-        <v>5.4945054945054949E-3</v>
+        <v>8.368200836820083E-3</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>119</v>
+      <c r="A25" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="13">
+        <v>2</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="H25" s="11">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I25" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17">
-        <f>SUM(D3:D25)</f>
-        <v>182</v>
-      </c>
-      <c r="E26" s="17">
-        <f>SUM(E3:E25)</f>
-        <v>22</v>
-      </c>
-      <c r="F26" s="17">
-        <f>SUM(F3:F25)</f>
+        <v>8.368200836820083E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" s="11">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="I26" s="12">
+        <f t="shared" si="1"/>
+        <v>8.368200836820083E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="13">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="I27" s="12">
+        <f t="shared" si="1"/>
+        <v>4.1841004184100415E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="I28" s="12">
+        <f t="shared" si="1"/>
+        <v>4.1841004184100415E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="13">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="I29" s="12">
+        <f t="shared" si="1"/>
+        <v>4.1841004184100415E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="9">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="I30" s="12">
+        <f t="shared" si="1"/>
+        <v>4.1841004184100415E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="11">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="I31" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H32" s="11">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17">
+        <f>SUM(D3:D32)</f>
+        <v>239</v>
+      </c>
+      <c r="E33" s="17">
+        <f>SUM(E3:E32)</f>
+        <v>29</v>
+      </c>
+      <c r="F33" s="17">
+        <f>SUM(F3:F32)</f>
         <v>9</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:I32" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I32">
+      <sortCondition descending="1" ref="D2:D32"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2398,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2408,78 +2634,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="A1" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="C3" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C4" s="22">
+        <v>4</v>
+      </c>
+      <c r="D4" s="20">
         <v>3</v>
-      </c>
-      <c r="D4" s="20">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C5" s="19">
+        <v>4</v>
+      </c>
+      <c r="D5" s="9">
         <v>3</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C6" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="20">
         <v>1</v>
@@ -2487,55 +2713,55 @@
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="C7" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="C8" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C9" s="19">
         <v>2</v>
       </c>
       <c r="D9" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C10" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="20">
         <v>2</v>
@@ -2543,24 +2769,24 @@
     </row>
     <row r="11" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="C11" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C12" s="22">
         <v>1</v>
@@ -2569,17 +2795,79 @@
         <v>2</v>
       </c>
     </row>
+    <row r="13" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="19">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="22">
+        <v>1</v>
+      </c>
+      <c r="D14" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1</v>
+      </c>
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="22">
+        <v>1</v>
+      </c>
+      <c r="D16" s="20">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D16">
+      <sortCondition descending="1" ref="C2"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2589,33 +2877,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="A1" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="23">
         <v>2</v>
@@ -2626,13 +2914,13 @@
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C4" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="24">
         <v>1</v>
@@ -2640,10 +2928,10 @@
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -2654,10 +2942,10 @@
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="C6" s="26">
         <v>1</v>
@@ -2668,10 +2956,10 @@
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C7" s="23">
         <v>1</v>
@@ -2682,10 +2970,10 @@
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="26">
         <v>1</v>
@@ -2696,10 +2984,10 @@
     </row>
     <row r="9" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="23">
         <v>1</v>
@@ -2710,10 +2998,10 @@
     </row>
     <row r="10" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="24" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" s="26">
         <v>1</v>
@@ -2722,17 +3010,37 @@
         <v>2</v>
       </c>
     </row>
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="23">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0001-0000-0400-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D11">
+      <sortCondition descending="1" ref="C2"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2740,34 +3048,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="A1" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="30">
         <v>29</v>
@@ -2779,12 +3087,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="30">
-        <v>19</v>
+        <f>_xlfn.XLOOKUP(A3,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B4" s="32">
         <v>24</v>
@@ -2796,192 +3105,386 @@
         <v>33</v>
       </c>
       <c r="E4" s="32">
-        <v>4</v>
+        <f>_xlfn.XLOOKUP(A4,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="33">
+        <v>56</v>
+      </c>
+      <c r="B5" s="30">
         <v>54</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="30">
         <v>46</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="30">
         <v>10</v>
       </c>
-      <c r="E5" s="33">
-        <v>13</v>
+      <c r="E5" s="30">
+        <f>_xlfn.XLOOKUP(A5,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="34">
+        <v>59</v>
+      </c>
+      <c r="B6" s="32">
         <v>65</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="32">
         <v>73</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="32">
         <v>4</v>
       </c>
-      <c r="E6" s="34">
-        <v>9</v>
+      <c r="E6" s="32">
+        <f>_xlfn.XLOOKUP(A6,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="35">
+        <v>71</v>
+      </c>
+      <c r="B7" s="30">
         <v>50</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="30">
         <v>69</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="30">
         <v>11</v>
       </c>
-      <c r="E7" s="35">
-        <v>13</v>
+      <c r="E7" s="30">
+        <f>_xlfn.XLOOKUP(A7,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="36">
+        <v>80</v>
+      </c>
+      <c r="B8" s="32">
         <v>27</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="32">
         <v>30</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="32">
         <v>3</v>
       </c>
-      <c r="E8" s="36">
-        <v>8</v>
+      <c r="E8" s="32">
+        <f>_xlfn.XLOOKUP(A8,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="38">
+        <v>52</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30">
         <v>20</v>
       </c>
-      <c r="E9" s="38">
-        <v>12</v>
+      <c r="E9" s="30">
+        <f>_xlfn.XLOOKUP(A9,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="39">
+        <v>65</v>
+      </c>
+      <c r="B10" s="32">
         <v>12</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="32">
         <v>49</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="32">
         <v>10</v>
       </c>
-      <c r="E10" s="39">
-        <v>11</v>
+      <c r="E10" s="32">
+        <f>_xlfn.XLOOKUP(A10,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="40">
+        <v>86</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30">
         <v>22</v>
       </c>
-      <c r="E11" s="40">
-        <v>6</v>
+      <c r="E11" s="30">
+        <f>_xlfn.XLOOKUP(A11,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="42">
+        <v>68</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32">
         <v>14</v>
       </c>
-      <c r="E12" s="42">
-        <v>13</v>
+      <c r="E12" s="32">
+        <f>_xlfn.XLOOKUP(A12,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="30">
         <v>5</v>
       </c>
       <c r="E13" s="30">
-        <v>12</v>
+        <f>_xlfn.XLOOKUP(A13,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
+        <v>83</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="32">
         <v>34</v>
       </c>
       <c r="E14" s="32">
+        <f>_xlfn.XLOOKUP(A14,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="33">
+        <v>77</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30">
         <v>2</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="30">
+        <f>_xlfn.XLOOKUP(A15,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="34">
-        <v>13</v>
+        <v>92</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32">
+        <f>_xlfn.XLOOKUP(A16,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="35">
-        <v>14</v>
+        <v>95</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30">
+        <f>_xlfn.XLOOKUP(A17,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32">
+        <f>_xlfn.XLOOKUP(A18,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30">
+        <f>_xlfn.XLOOKUP(A19,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32">
+        <f>_xlfn.XLOOKUP(A20,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30">
+        <f>_xlfn.XLOOKUP(A21,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32">
+        <f>_xlfn.XLOOKUP(A22,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30">
+        <f>_xlfn.XLOOKUP(A23,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32">
+        <f>_xlfn.XLOOKUP(A24,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30">
+        <f>_xlfn.XLOOKUP(A25,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32">
+        <f>_xlfn.XLOOKUP(A26,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30">
+        <f>_xlfn.XLOOKUP(A27,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32">
+        <f>_xlfn.XLOOKUP(A28,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30">
+        <f>_xlfn.XLOOKUP(A29,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32">
+        <f>_xlfn.XLOOKUP(A30,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30">
+        <f>_xlfn.XLOOKUP(A31,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32">
+        <f>_xlfn.XLOOKUP(A32,'🟥 Jogadores_Mes'!A:A,'🟥 Jogadores_Mes'!D:D)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Pelada_do_Filhao.xlsx
+++ b/Pelada_do_Filhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\85223166\Desktop\Controle Pelada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF987D0-EF45-400D-8399-09E9C91B463D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B1453C-903D-43EB-B6C5-6AEF066D1D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="⚙️ Config" sheetId="2" r:id="rId1"/>
@@ -748,7 +748,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -826,6 +826,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -854,7 +860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -958,16 +964,22 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -977,11 +989,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1297,10 +1306,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="38"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="4" t="s">
@@ -1354,7 +1363,7 @@
       <c r="B8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="38">
         <v>46163</v>
       </c>
     </row>
@@ -1380,13 +1389,13 @@
       <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="38"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="38"/>
+      <c r="B2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="40"/>
     </row>
     <row r="4" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
@@ -1498,14 +1507,14 @@
     <col min="2" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="41" t="s">
+    <row r="1" spans="2:4" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-    </row>
-    <row r="2" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+    </row>
+    <row r="2" spans="2:4" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="33" t="s">
         <v>130</v>
       </c>
@@ -1615,18 +1624,18 @@
     <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:9" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
@@ -2154,7 +2163,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="37" t="s">
         <v>144</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -2185,7 +2194,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="37" t="s">
         <v>137</v>
       </c>
       <c r="B20" s="13" t="s">
@@ -2340,7 +2349,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="37" t="s">
         <v>139</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2371,7 +2380,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="37" t="s">
         <v>146</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -2402,7 +2411,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="37" t="s">
         <v>141</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -2433,7 +2442,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="37" t="s">
         <v>145</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -2526,7 +2535,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="37" t="s">
         <v>140</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -2633,13 +2642,13 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:4" ht="3.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
@@ -2648,7 +2657,7 @@
       <c r="B2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="46" t="s">
         <v>43</v>
       </c>
       <c r="D2" s="18" t="s">
@@ -2877,12 +2886,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
@@ -3048,13 +3057,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
